--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_VSC.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_VSC.xlsx
@@ -422,11 +422,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -515,91 +515,247 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VSC_D._RUNGE</t>
+          <t>VSC_M._DRUMWRIGHT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>M. Drumwright</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VSC_T._SIMAO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>T. Simao</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>32.1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VSC_D._RUNGE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D. Runge</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VSC_A._GUEDES</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A. Guedes</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>27.8</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -616,24 +772,169 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>players</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pf_per40</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pa_per40</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>net_per40</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Most used</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>M. Drumwright | R. Stein</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-2.8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Best defense</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>D. Runge | M. Drumwright</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Best net</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>D. Runge | M. Drumwright</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>trio</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Most used</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>M. Drumwright | R. Stein | T. Simao</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-4.3</v>
       </c>
     </row>
   </sheetData>
@@ -787,7 +1088,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
     </row>
@@ -863,16 +1164,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73.7</v>
+        <v>80.8</v>
       </c>
       <c r="C2" t="n">
-        <v>76.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="3">
@@ -882,16 +1183,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>112.3</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>110.4</v>
+        <v>106.2</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9</v>
+        <v>-10.3</v>
       </c>
     </row>
     <row r="4">
@@ -901,16 +1202,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>106</v>
+        <v>101.4</v>
       </c>
       <c r="C4" t="n">
-        <v>110.4</v>
+        <v>106.6</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.4</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="5">
@@ -920,16 +1221,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.4</v>
+        <v>-5.5</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>6.4</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="6">
@@ -939,16 +1240,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="7">
@@ -958,13 +1259,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C7" t="n">
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>-0</v>
@@ -977,13 +1278,13 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C8" t="n">
         <v>0.3</v>
       </c>
-      <c r="C8" t="n">
-        <v>0.4</v>
-      </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
         <v>-0.1</v>
@@ -996,16 +1297,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>21.3</v>
+        <v>20.8</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.3</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="10">
@@ -1021,7 +1322,7 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
         <v>0.1</v>
@@ -1040,7 +1341,7 @@
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>-0</v>
@@ -1084,7 +1385,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Below-average pace; they are more comfortable when the game stays organized in the half court.</t>
+          <t>Above-average pace; expect a game that can speed up if you allow early flow.</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1487,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Control the rhythm: they are more comfortable in a controlled half-court game, so do not let them play cleanly into structure.</t>
+          <t>Set the tempo early: if you let them run into flow, the game can speed up on their terms.</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1264,7 +1565,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The main offensive references are R. Stein and D. Runge; load the scouting plan into those names first.</t>
+          <t>The main offensive references are R. Stein and M. Drumwright; load the scouting plan into those names first.</t>
         </is>
       </c>
     </row>
@@ -1276,19 +1577,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from M. Drumwright and T. Simao; contest, but do not over-help into secondary advantages.</t>
+          <t>Priority closeouts start with D. Runge; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Scoring Areas</t>
+          <t>Perimeter Shooting</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Their offense naturally flows toward Paint Non-RA; protect that area early in possessions.</t>
+          <t>Some perimeter volume comes from R. Stein and M. Drumwright; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
@@ -1300,19 +1601,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially D. Runge, M. Drumwright, and T. Simao; force them away from preferred areas.</t>
+          <t>Their offense naturally flows toward Restricted Area; protect that area early in possessions.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Units</t>
+          <t>Scoring Areas</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Most-used lineup to rehearse first: A. Guedes | D. Runge | M. Drumwright | R. Stein | T. Simao.</t>
+          <t>Several players have clear comfort zones, especially T. Simao, D. Runge, and M. Houge; force them away from preferred areas.</t>
         </is>
       </c>
     </row>
@@ -1324,19 +1625,55 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Secondary lineup to recognize: A. Guedes | D. Runge | M. Drumwright | R. Stein | T. Simao.</t>
+          <t>Most-used lineup to rehearse first: A. Guedes | D. Runge | M. Drumwright | R. Stein | T. Simao.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Secondary lineup to recognize: A. Guedes | D. Runge | M. Drumwright | R. Stein | T. Simao.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Recognize the main duo/trio combinations: M. Drumwright | R. Stein and D. Runge | M. Drumwright.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Defensive Emphasis</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Limited offensive rebounding impact; finishing the first contest usually kills the possession.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Defensive Emphasis</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Do not lose D. Runge in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1351,11 +1688,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -1418,22 +1755,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>38.3</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1445,36 +1782,144 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>VSC_M._DRUMWRIGHT</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>M. Drumwright</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>primary handler</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VSC_T._SIMAO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>T. Simao</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>paint finisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>VSC_D._RUNGE</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>D. Runge</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>40</v>
-      </c>
-      <c r="D3" t="n">
-        <v>15</v>
-      </c>
-      <c r="E3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="C5" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>primary scorer</t>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>rotation piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VSC_A._GUEDES</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A. Guedes</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>rotation piece</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1500,7 +1945,7 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -1583,41 +2028,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VSC_M._DRUMWRIGHT</t>
+          <t>VSC_D._RUNGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>M. Drumwright</t>
+          <t>D. Runge</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -1634,32 +2079,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VSC_T._SIMAO</t>
+          <t>VSC_R._STEIN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T. Simao</t>
+          <t>R. Stein</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1680,29 +2125,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VSC_R._COSTA</t>
+          <t>VSC_M._DRUMWRIGHT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>R. Costa</t>
+          <t>M. Drumwright</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="H4" t="n">
         <v>0.7</v>
@@ -1721,74 +2166,94 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VSC_R._COSTA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R. Costa</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>47.1%</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>26.6%</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>17</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>23.5%</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>26.6%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>VSC_S._VERDE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>S. Verde</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1810,19 +2275,19 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>32.8%</t>
         </is>
       </c>
     </row>
@@ -1842,23 +2307,23 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>28.1%</t>
         </is>
       </c>
     </row>
@@ -1878,42 +2343,34 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>18.8%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>VSC_D._RUNGE</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>D. Runge</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -1922,42 +2379,34 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>10.9%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>VSC_M._DRUMWRIGHT</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>M. Drumwright</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -1966,23 +2415,23 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>6.2%</t>
         </is>
       </c>
     </row>
@@ -2014,19 +2463,283 @@
         </is>
       </c>
       <c r="K12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VSC_D._RUNGE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>D. Runge</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>9</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>56.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VSC_M._HOUGE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>M. Houge</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>88.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>VSC_K._WARNER</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>K. Warner</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>VSC_M._DRUMWRIGHT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>M. Drumwright</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>34.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>VSC_R._STEIN</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>R. Stein</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
         <v>6</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>46.2%</t>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>VSC_A._GUEDES</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>A. Guedes</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>5</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>33.3%</t>
         </is>
       </c>
     </row>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_VSC.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_VSC.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -515,41 +515,41 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
     </row>
@@ -567,41 +567,41 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
     </row>
@@ -619,53 +619,53 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VSC_D._RUNGE</t>
+          <t>VSC_K._WARNER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -675,32 +675,32 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>35.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -712,50 +712,154 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VSC_A._GUEDES</t>
+          <t>VSC_D._RUNGE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A. Guedes</t>
+          <t>D. Runge</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>23.4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VSC_A._GUEDES</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A. Guedes</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VSC_M._HOUGE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>M. Houge</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
         <v>2</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>27.8</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -838,16 +942,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>70.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="E2" t="n">
         <v>77.90000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>80.7</v>
+        <v>82.8</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.8</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="3">
@@ -863,78 +967,78 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>D. Runge | M. Drumwright</t>
+          <t>M. Drumwright | T. Simao</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>56.2</v>
+        <v>77</v>
       </c>
       <c r="E3" t="n">
-        <v>82.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>74.7</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>7.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>duo</t>
+          <t>trio</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Best net</t>
+          <t>Most used</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>D. Runge | M. Drumwright</t>
+          <t>M. Drumwright | R. Stein | T. Simao</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>56.2</v>
+        <v>73.3</v>
       </c>
       <c r="E4" t="n">
-        <v>82.5</v>
+        <v>83</v>
       </c>
       <c r="F4" t="n">
-        <v>74.7</v>
+        <v>83</v>
       </c>
       <c r="G4" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>trio</t>
+          <t>duo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Most used</t>
+          <t>Best net</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>M. Drumwright | R. Stein | T. Simao</t>
+          <t>D. Runge | R. Stein</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>55.9</v>
+        <v>68.2</v>
       </c>
       <c r="E5" t="n">
-        <v>77.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>82.2</v>
+        <v>83.3</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.3</v>
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
@@ -1037,7 +1141,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>R. Stein</t>
+          <t>K. Warner</t>
         </is>
       </c>
     </row>
@@ -1164,13 +1268,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>2.1</v>
@@ -1183,16 +1287,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>95.90000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>106.2</v>
+        <v>105.6</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>-10.3</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="4">
@@ -1202,16 +1306,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>101.4</v>
+        <v>104.9</v>
       </c>
       <c r="C4" t="n">
-        <v>106.6</v>
+        <v>105.9</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>-5.2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
@@ -1221,16 +1325,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-5.5</v>
+        <v>-11.3</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>-5.1</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="6">
@@ -1240,16 +1344,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.2</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="7">
@@ -1259,13 +1363,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C7" t="n">
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>-0</v>
@@ -1297,16 +1401,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="10">
@@ -1316,16 +1420,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C10" t="n">
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
@@ -1341,7 +1445,7 @@
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>-0</v>
@@ -1523,7 +1627,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Load into R. Stein: he is the main organizer, so make secondary creators finish possessions.</t>
+          <t>Know the first reference: K. Warner is a primary scorer, and the plan should start with taking away his comfort.</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1681,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priority closeouts start with D. Runge; do not lose them in help-and-recover situations.</t>
+          <t>Priority closeouts start with D. Runge, R. Stein, and K. Warner; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1693,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from R. Stein and M. Drumwright; contest, but do not over-help into secondary advantages.</t>
+          <t>Some perimeter volume comes from K. Warner and R. Stein; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1717,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially T. Simao, D. Runge, and M. Houge; force them away from preferred areas.</t>
+          <t>Several players have clear comfort zones, especially K. Warner, T. Simao, and M. Houge; force them away from preferred areas.</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1753,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Recognize the main duo/trio combinations: M. Drumwright | R. Stein and D. Runge | M. Drumwright.</t>
+          <t>Recognize the main duo/trio combinations: M. Drumwright | R. Stein and M. Drumwright | T. Simao.</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1777,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Do not lose D. Runge in help-and-recover situations.</t>
+          <t>Do not lose D. Runge and R. Stein in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1755,17 +1859,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38.3</v>
+        <v>38</v>
       </c>
       <c r="D2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1775,7 +1879,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>primary handler</t>
+          <t>paint finisher</t>
         </is>
       </c>
     </row>
@@ -1791,17 +1895,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37.1</v>
+        <v>34.3</v>
       </c>
       <c r="D3" t="n">
-        <v>10.5</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1827,10 +1931,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32.1</v>
+        <v>31.3</v>
       </c>
       <c r="D4" t="n">
-        <v>11.5</v>
+        <v>10.3</v>
       </c>
       <c r="E4" t="n">
         <v>6</v>
@@ -1854,26 +1958,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VSC_D._RUNGE</t>
+          <t>VSC_K._WARNER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.5</v>
+        <v>35.4</v>
       </c>
       <c r="D5" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1883,41 +1987,77 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>primary scorer</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>VSC_D._RUNGE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>D. Runge</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>rotation piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>VSC_A._GUEDES</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>A. Guedes</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="C7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E7" t="n">
         <v>8</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>rotation piece</t>
         </is>
@@ -1934,7 +2074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -2051,11 +2191,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -2074,7 +2214,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2088,20 +2228,20 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -2120,41 +2260,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VSC_M._DRUMWRIGHT</t>
+          <t>VSC_K._WARNER</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>M. Drumwright</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -2171,36 +2311,36 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VSC_R._COSTA</t>
+          <t>VSC_K._WARNER</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>R. Costa</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -2217,36 +2357,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VSC_S._VERDE</t>
+          <t>VSC_R._STEIN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>S. Verde</t>
+          <t>R. Stein</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>27.8%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>36</v>
+      </c>
+      <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -2258,74 +2398,94 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>42</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>59.5%</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>32.8%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>VSC_R._COSTA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>R. Costa</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>36</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>30.6%</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>28.1%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>VSC_S._VERDE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>S. Verde</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2343,23 +2503,23 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>35.1%</t>
         </is>
       </c>
     </row>
@@ -2379,23 +2539,23 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>27.3%</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2575,34 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>20.5%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>VSC_T._SIMAO</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>T. Simao</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -2459,15 +2611,15 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -2475,26 +2627,18 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>VSC_D._RUNGE</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>D. Runge</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -2503,23 +2647,23 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>4.9%</t>
         </is>
       </c>
     </row>
@@ -2531,12 +2675,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VSC_M._HOUGE</t>
+          <t>VSC_K._WARNER</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>M. Houge</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -2547,23 +2691,23 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>55.9%</t>
         </is>
       </c>
     </row>
@@ -2575,12 +2719,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VSC_K._WARNER</t>
+          <t>VSC_T._SIMAO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>K. Warner</t>
+          <t>T. Simao</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2591,23 +2735,23 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -2619,12 +2763,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VSC_M._DRUMWRIGHT</t>
+          <t>VSC_M._HOUGE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>M. Drumwright</t>
+          <t>M. Houge</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -2635,23 +2779,23 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>68.2%</t>
         </is>
       </c>
     </row>
@@ -2683,19 +2827,19 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2851,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>VSC_A._GUEDES</t>
+          <t>VSC_M._DRUMWRIGHT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A. Guedes</t>
+          <t>M. Drumwright</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2723,21 +2867,109 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>13</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>15.4%</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>35.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>VSC_D._RUNGE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>D. Runge</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="K18" t="n">
+      <c r="K19" t="n">
+        <v>9</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>52.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>VSC_A._GUEDES</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>A. Guedes</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
         <v>5</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>20.0%</t>
         </is>
       </c>
-      <c r="M18" t="n">
+      <c r="M20" t="n">
         <v>0.6</v>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>33.3%</t>
         </is>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_VSC.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_VSC.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -515,11 +515,11 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -529,27 +529,27 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -567,41 +567,41 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -619,41 +619,41 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -671,21 +671,21 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -695,12 +695,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -723,36 +723,36 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -775,7 +775,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -784,27 +784,27 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -827,39 +827,91 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VSC_S._VERDE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>S. Verde</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -942,74 +994,74 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>98.59999999999999</v>
+        <v>127.3</v>
       </c>
       <c r="E2" t="n">
-        <v>77.90000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="F2" t="n">
-        <v>82.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>duo</t>
+          <t>trio</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Best defense</t>
+          <t>Most used</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>M. Drumwright | T. Simao</t>
+          <t>M. Drumwright | R. Stein | T. Simao</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>77</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>82.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="F3" t="n">
-        <v>81.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>trio</t>
+          <t>duo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Most used</t>
+          <t>Best defense</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>M. Drumwright | R. Stein | T. Simao</t>
+          <t>A. Guedes | M. Drumwright</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>73.3</v>
+        <v>64.8</v>
       </c>
       <c r="E4" t="n">
-        <v>83</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>83</v>
+        <v>72.2</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="5">
@@ -1025,20 +1077,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>D. Runge | R. Stein</t>
+          <t>A. Guedes | M. Drumwright</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>68.2</v>
+        <v>64.8</v>
       </c>
       <c r="E5" t="n">
-        <v>84.40000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>83.3</v>
+        <v>72.2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2</v>
+        <v>11.7</v>
       </c>
     </row>
   </sheetData>
@@ -1141,7 +1193,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>K. Warner</t>
+          <t>R. Stein</t>
         </is>
       </c>
     </row>
@@ -1268,16 +1320,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80.90000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="C2" t="n">
-        <v>78.8</v>
+        <v>79.3</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="3">
@@ -1287,16 +1339,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>93.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="C3" t="n">
-        <v>105.6</v>
+        <v>103.9</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>-12</v>
+        <v>-10.1</v>
       </c>
     </row>
     <row r="4">
@@ -1306,16 +1358,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>104.9</v>
+        <v>101.9</v>
       </c>
       <c r="C4" t="n">
-        <v>105.9</v>
+        <v>104</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>-1</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="5">
@@ -1325,16 +1377,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-11.3</v>
+        <v>-8</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>-11</v>
+        <v>-7.9</v>
       </c>
     </row>
     <row r="6">
@@ -1344,16 +1396,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="C6" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.4</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="7">
@@ -1363,13 +1415,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C7" t="n">
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>-0</v>
@@ -1388,7 +1440,7 @@
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>-0.1</v>
@@ -1401,16 +1453,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20.8</v>
       </c>
       <c r="C9" t="n">
         <v>20.7</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1420,16 +1472,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C10" t="n">
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1445,7 +1497,7 @@
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>-0</v>
@@ -1489,7 +1541,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Above-average pace; expect a game that can speed up if you allow early flow.</t>
+          <t>League-average pace; rhythm control matters more than pure speed against them.</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1589,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lower foul volume than league average; this is not a team that wants constant contact chaos.</t>
+          <t>Foul profile sits near league average; physicality is part of the game, but not their defining trait.</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1601,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Less three-point dependent than league average; more of their offense is built away from pure perimeter volume.</t>
+          <t>Perimeter volume is close to league average; shot mix alone does not define them.</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1643,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Set the tempo early: if you let them run into flow, the game can speed up on their terms.</t>
+          <t>Own the rhythm: pace itself is not the main separator, so the quality of possessions matters more than speed.</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1667,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Do not overreact to the arc: make them finish over traffic instead of giving up easy paint comfort.</t>
+          <t>Know the first reference: R. Stein is a paint finisher, and the plan should start with taking away his comfort.</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Know the first reference: K. Warner is a primary scorer, and the plan should start with taking away his comfort.</t>
+          <t>Closeout discipline matters: M. Drumwright, R. Stein are the first perimeter names you cannot lose in help situations.</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1733,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priority closeouts start with D. Runge, R. Stein, and K. Warner; do not lose them in help-and-recover situations.</t>
+          <t>Priority closeouts start with M. Drumwright, R. Stein, and D. Runge; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1745,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from K. Warner and R. Stein; contest, but do not over-help into secondary advantages.</t>
+          <t>Some perimeter volume comes from K. Warner and A. Guedes; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1805,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Recognize the main duo/trio combinations: M. Drumwright | R. Stein and M. Drumwright | T. Simao.</t>
+          <t>Recognize the main duo/trio combinations: M. Drumwright | R. Stein and M. Drumwright | R. Stein | T. Simao.</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1829,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Do not lose D. Runge and R. Stein in help-and-recover situations.</t>
+          <t>Do not lose M. Drumwright and R. Stein in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1859,17 +1911,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38</v>
+        <v>37.5</v>
       </c>
       <c r="D2" t="n">
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1895,13 +1947,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34.3</v>
+        <v>33.6</v>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>11.5</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1910,7 +1962,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1931,17 +1983,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31.3</v>
+        <v>27.7</v>
       </c>
       <c r="D4" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1967,17 +2019,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>35.4</v>
+        <v>31.1</v>
       </c>
       <c r="D5" t="n">
-        <v>16.5</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2003,17 +2055,17 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.4</v>
+        <v>22.4</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2023,7 +2075,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
@@ -2042,14 +2094,14 @@
         <v>19.5</v>
       </c>
       <c r="D7" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2059,7 +2111,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -2173,36 +2225,36 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VSC_D._RUNGE</t>
+          <t>VSC_M._DRUMWRIGHT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>M. Drumwright</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -2228,23 +2280,23 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2265,32 +2317,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VSC_K._WARNER</t>
+          <t>VSC_D._RUNGE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>K. Warner</t>
+          <t>D. Runge</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2306,37 +2358,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VSC_K._WARNER</t>
+          <t>VSC_A._GUEDES</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>K. Warner</t>
+          <t>A. Guedes</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2357,16 +2409,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VSC_R._STEIN</t>
+          <t>VSC_K._WARNER</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>R. Stein</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2375,18 +2427,18 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -2403,36 +2455,36 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VSC_R._COSTA</t>
+          <t>VSC_A._GUEDES</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>R. Costa</t>
+          <t>A. Guedes</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -2458,27 +2510,27 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -2490,38 +2542,48 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>72</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>52.8%</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>35.1%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VSC_R._COSTA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>R. Costa</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2539,23 +2601,23 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
     </row>
@@ -2575,23 +2637,23 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>28.9%</t>
         </is>
       </c>
     </row>
@@ -2611,15 +2673,15 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -2627,7 +2689,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
     </row>
@@ -2647,42 +2709,34 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>8.1%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>VSC_K._WARNER</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>K. Warner</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -2691,23 +2745,23 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>5.2%</t>
         </is>
       </c>
     </row>
@@ -2719,12 +2773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VSC_T._SIMAO</t>
+          <t>VSC_K._WARNER</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>T. Simao</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2735,23 +2789,23 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>59.5%</t>
         </is>
       </c>
     </row>
@@ -2763,12 +2817,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VSC_M._HOUGE</t>
+          <t>VSC_T._SIMAO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>M. Houge</t>
+          <t>T. Simao</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -2783,19 +2837,19 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>55.0%</t>
         </is>
       </c>
     </row>
@@ -2807,12 +2861,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>VSC_R._STEIN</t>
+          <t>VSC_M._HOUGE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>R. Stein</t>
+          <t>M. Houge</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -2827,19 +2881,19 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -2851,12 +2905,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>VSC_M._DRUMWRIGHT</t>
+          <t>VSC_R._STEIN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>M. Drumwright</t>
+          <t>R. Stein</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2867,23 +2921,23 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>41.9%</t>
         </is>
       </c>
     </row>
@@ -2895,12 +2949,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VSC_D._RUNGE</t>
+          <t>VSC_M._DRUMWRIGHT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>M. Drumwright</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -2911,15 +2965,15 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M19" t="n">
@@ -2927,7 +2981,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
     </row>
@@ -2939,12 +2993,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VSC_A._GUEDES</t>
+          <t>VSC_D._RUNGE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A. Guedes</t>
+          <t>D. Runge</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -2959,19 +3013,107 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>VSC_S._VERDE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>S. Verde</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>38.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>VSC_A._GUEDES</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>A. Guedes</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>6</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
